--- a/Luban/Config/Datas/Levels/L19/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L19/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L19 W1/25; N=49; EHP=308.308000; normal:17x24,normal:18x25</t>
+          <t>L19 W1/25; N=49; EHP=788.052784; normal:17x24,normal:18x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L19 W2/25; N=55; EHP=362.359426; normal:17x28,normal:18x27</t>
+          <t>L19 W2/25; N=55; EHP=926.211303; normal:17x28,normal:18x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3824136,3824673,3824019,3824136,3824673,3824019,3824136,3824673,3824091,3824136,3824673,3824099,3824136,3824673,3824099,3824136,3824673,3824107,3824136,3824673,3824115,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144</t>
+          <t>3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824673,3824136,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144,3824144</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L19 W3/25; N=61; EHP=444.607821; air:2x2,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x18,normal:18x19,swarm:84x17</t>
+          <t>L19 W3/25; N=61; EHP=1221.898055; normal:17x18,normal:18x26,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3826136,3826673,3826019,3826136,3826673,3826019,3826136,3826673,3826091,3826136,3826673,3826091,3826136,3826673,3826099,3826136,3826673,3826107,3826136,3826673,3826107,3826136,3826673,3826115,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826136,3826136,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144</t>
+          <t>3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826673,3826136,3826136,3826136,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826144,3826136,3826136,3826136,3826136,3826136,3826136,3826136,3826136</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L19 W4/25; N=67; EHP=562.324220; air:2x2,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x21,normal:18x20,swarm:84x18</t>
+          <t>L19 W4/25; N=67; EHP=1549.664195; normal:17x29,normal:18x20,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3828136,3828673,3828019,3828668,3828136,3828673,3828091,3828668,3828136,3828673,3828091,3828668,3828136,3828673,3828099,3828668,3828136,3828673,3828099,3828868,3828136,3828673,3828107,3828868,3828136,3828673,3828107,3828868,3828136,3828673,3828115,3828988,3828136,3828673,3828115,3828988,3828136,3828673,3828988,3828136,3828673,3828136,3828673,3828136,3828673,3828136,3828673,3828136,3828673,3828136,3828673,3828136,3828673,3828144,3828673,3828144,3828673,3828144,3828673,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144</t>
+          <t>3828136,3828019,3828019,3828668,3828136,3828091,3828091,3828668,3828136,3828091,3828091,3828668,3828136,3828099,3828099,3828668,3828136,3828099,3828099,3828868,3828136,3828107,3828107,3828868,3828136,3828107,3828107,3828868,3828136,3828115,3828115,3828988,3828136,3828115,3828115,3828988,3828136,3828673,3828988,3828136,3828673,3828136,3828673,3828136,3828673,3828136,3828673,3828136,3828673,3828136,3828673,3828136,3828673,3828144,3828673,3828144,3828673,3828144,3828673,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144,3828144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L19 W5/25; N=73; EHP=1055.258300; air:2x1,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x17,normal:18x17,medium:83x4,swarm:84x20,medium:108x3,medium:123x3</t>
+          <t>L19 W5/25; N=73; EHP=2732.973566; air:2x2,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x4,medium:108x3,medium:123x3,normal:17x17,normal:18x17,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3830136,3830673,3830242,3830019,3830668,3830136,3830673,3830242,3830019,3830668,3830136,3830673,3830466,3830091,3830668,3830136,3830673,3830466,3830091,3830868,3830136,3830673,3830514,3830099,3830868,3830136,3830673,3830514,3830099,3830868,3830136,3830673,3830786,3830107,3830868,3830136,3830673,3830786,3830115,3830988,3830136,3830673,3830786,3830115,3830988,3830136,3830673,3830988,3830136,3830673,3830988,3830136,3830673,3830136,3830673,3830136,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830144,3830144,3830144,3830144,3830144</t>
+          <t>3830136,3830019,3830242,3830019,3830668,3830136,3830019,3830242,3830019,3830668,3830136,3830091,3830466,3830091,3830668,3830136,3830091,3830466,3830091,3830868,3830136,3830099,3830514,3830099,3830868,3830136,3830099,3830514,3830099,3830868,3830136,3830107,3830786,3830107,3830868,3830136,3830115,3830786,3830115,3830988,3830136,3830115,3830786,3830115,3830988,3830136,3830673,3830988,3830136,3830673,3830988,3830136,3830673,3830136,3830673,3830136,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830673,3830144,3830144,3830144,3830144,3830144,3830144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L19 W6/25; N=79; EHP=1077.000000; air:2x2,air:11x2,air:12x2,air:13x1,air:14x2,normal:17x14,normal:18x14,fast:30x2,fast:58x2,fast:64x2,medium:83x3,swarm:84x22,fast:98x3,medium:108x4,medium:123x4</t>
+          <t>L19 W6/25; N=79; EHP=2786.952843; air:2x4,air:11x4,air:12x4,air:13x2,air:14x4,fast:30x2,fast:58x2,fast:64x2,fast:98x3,medium:83x3,medium:108x4,medium:123x4,normal:17x14,normal:18x14,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3832136,3832673,3832242,3832019,3832668,3832136,3832673,3832242,3832019,3832668,3832136,3832673,3832466,3832091,3832668,3832136,3832673,3832466,3832091,3832668,3832136,3832673,3832466,3832099,3832868,3832136,3832673,3832514,3832099,3832868,3832136,3832673,3832514,3832107,3832868,3832136,3832673,3832514,3832107,3832868,3832136,3832673,3832786,3832115,3832988,3832136,3832673,3832786,3832115,3832988,3832136,3832673,3832988,3832136,3832673,3832988,3832136,3832673,3832136,3832673,3832136,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832144,3832144,3832144,3832144,3832144,3832144</t>
+          <t>3832136,3832019,3832242,3832019,3832668,3832136,3832019,3832242,3832019,3832668,3832136,3832091,3832466,3832091,3832668,3832136,3832091,3832466,3832091,3832668,3832136,3832099,3832466,3832099,3832868,3832136,3832099,3832514,3832099,3832868,3832136,3832107,3832514,3832107,3832868,3832136,3832107,3832514,3832107,3832868,3832136,3832115,3832786,3832115,3832988,3832136,3832115,3832786,3832115,3832988,3832136,3832673,3832988,3832136,3832673,3832988,3832136,3832673,3832136,3832673,3832136,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832673,3832144,3832144,3832144,3832144,3832144,3832144,3832144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L19 W7/25; N=85; EHP=1208.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x2,fast:58x3,fast:64x3,medium:83x4,swarm:84x23,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L19 W7/25; N=85; EHP=3127.125982; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x13 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3834136,3834673,3834242,3834019,3834668,3834136,3834673,3834242,3834019,3834668,3834136,3834673,3834242,3834091,3834668,3834136,3834673,3834466,3834091,3834668,3834136,3834673,3834466,3834099,3834668,3834136,3834673,3834514,3834099,3834868,3834136,3834673,3834514,3834099,3834868,3834136,3834673,3834514,3834107,3834868,3834136,3834673,3834786,3834107,3834868,3834136,3834673,3834786,3834115,3834988,3834136,3834673,3834115,3834988,3834136,3834673,3834988,3834136,3834673,3834988,3834136,3834673,3834136,3834673,3834136,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834144,3834144,3834144,3834144,3834144,3834144</t>
+          <t>3834136,3834019,3834242,3834019,3834668,3834136,3834019,3834242,3834019,3834668,3834136,3834091,3834242,3834091,3834668,3834136,3834091,3834466,3834091,3834668,3834136,3834099,3834466,3834099,3834668,3834136,3834099,3834514,3834099,3834868,3834136,3834099,3834514,3834099,3834868,3834136,3834107,3834514,3834107,3834868,3834136,3834107,3834786,3834107,3834868,3834136,3834115,3834786,3834115,3834988,3834136,3834115,3834115,3834988,3834136,3834673,3834988,3834136,3834673,3834988,3834136,3834673,3834136,3834673,3834136,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834673,3834144,3834144,3834144,3834144,3834144,3834144,3834144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L19 W8/25; N=91; EHP=1553.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x16,normal:18x16,fast:30x3,fast:58x2,fast:64x3,medium:83x5,swarm:84x25,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L19 W8/25; N=91; EHP=4021.662678; air:2x4,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x2,medium:83x5,medium:108x4,medium:123x4,normal:17x16,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3836136,3836673,3836242,3836019,3836668,3836136,3836673,3836242,3836019,3836668,3836136,3836673,3836242,3836019,3836668,3836136,3836673,3836466,3836091,3836668,3836136,3836673,3836466,3836091,3836868,3836136,3836673,3836466,3836099,3836868,3836136,3836673,3836514,3836099,3836868,3836136,3836673,3836514,3836107,3836868,3836136,3836673,3836786,3836107,3836868,3836136,3836673,3836786,3836107,3836988,3836136,3836673,3836786,3836115,3836988,3836136,3836673,3836115,3836988,3836136,3836673,3836988,3836136,3836673,3836988,3836136,3836673,3836136,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836144,3836144,3836144,3836144,3836144</t>
+          <t>3836136,3836019,3836242,3836019,3836668,3836136,3836019,3836242,3836019,3836668,3836136,3836019,3836242,3836019,3836668,3836136,3836091,3836466,3836091,3836668,3836136,3836091,3836466,3836091,3836868,3836136,3836099,3836466,3836099,3836868,3836136,3836099,3836514,3836099,3836868,3836136,3836107,3836514,3836107,3836868,3836136,3836107,3836786,3836107,3836868,3836136,3836107,3836786,3836107,3836988,3836136,3836115,3836786,3836115,3836988,3836136,3836115,3836115,3836988,3836136,3836673,3836988,3836136,3836673,3836988,3836136,3836673,3836136,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836673,3836144,3836144,3836144,3836144,3836144,3836144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L19 W9/25; N=97; EHP=1982.000000; air:2x3,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x16,normal:18x17,fast:30x3,fast:58x3,fast:64x2,medium:83x4,swarm:84x27,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L19 W9/25; N=97; EHP=5134.335097; air:2x6,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x2,fast:98x3,medium:83x4,medium:108x5,medium:123x5,normal:17x16,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3838136,3838673,3838242,3838019,3838668,3838136,3838673,3838242,3838019,3838668,3838136,3838673,3838242,3838091,3838668,3838136,3838673,3838466,3838091,3838668,3838136,3838673,3838466,3838091,3838668,3838136,3838673,3838466,3838099,3838868,3838136,3838673,3838514,3838099,3838868,3838136,3838673,3838514,3838107,3838868,3838136,3838673,3838514,3838107,3838868,3838136,3838673,3838786,3838107,3838868,3838136,3838673,3838786,3838115,3838988,3838136,3838673,3838786,3838115,3838988,3838136,3838673,3838988,3838136,3838673,3838988,3838136,3838673,3838988,3838136,3838673,3838136,3838673,3838136,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838144,3838144,3838144,3838144,3838144,3838144,3838144</t>
+          <t>3838136,3838019,3838242,3838019,3838668,3838136,3838019,3838242,3838019,3838668,3838136,3838091,3838242,3838091,3838668,3838136,3838091,3838466,3838091,3838668,3838136,3838091,3838466,3838091,3838668,3838136,3838099,3838466,3838099,3838868,3838136,3838099,3838514,3838099,3838868,3838136,3838107,3838514,3838107,3838868,3838136,3838107,3838514,3838107,3838868,3838136,3838107,3838786,3838107,3838868,3838136,3838115,3838786,3838115,3838988,3838136,3838115,3838786,3838115,3838988,3838136,3838673,3838988,3838136,3838673,3838988,3838136,3838673,3838988,3838136,3838673,3838136,3838673,3838136,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838673,3838144,3838144,3838144,3838144,3838144,3838144,3838144,3838144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L19 W10/25; N=103; EHP=3654.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x18,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x28,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L19 W10/25; N=103; EHP=9457.437265; air:2x4,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x18,normal:18x18,swarm:84x16 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3840136,3840673,3840242,3840019,3840668,3840253,3840136,3840673,3840242,3840019,3840668,3840325,3840136,3840673,3840242,3840091,3840668,3840541,3840136,3840673,3840466,3840091,3840668,3840541,3840136,3840673,3840466,3840091,3840668,3840565,3840136,3840673,3840466,3840099,3840668,3840565,3840136,3840673,3840466,3840099,3840868,3840645,3840136,3840673,3840514,3840099,3840868,3840693,3840136,3840673,3840514,3840107,3840868,3840709,3840136,3840673,3840514,3840107,3840868,3841021,3840136,3840673,3840786,3840115,3840868,3840136,3840673,3840786,3840115,3840988,3840136,3840673,3840786,3840115,3840988,3840144,3840673,3840988,3840144,3840673,3840988,3840144,3840673,3840988,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840673,3840673,3840673</t>
+          <t>3840136,3840019,3840242,3840019,3840668,3840253,3840136,3840019,3840242,3840019,3840668,3840325,3840136,3840091,3840242,3840091,3840668,3840541,3840136,3840091,3840466,3840091,3840668,3840541,3840136,3840091,3840466,3840091,3840668,3840565,3840136,3840099,3840466,3840099,3840668,3840565,3840136,3840099,3840466,3840099,3840868,3840645,3840136,3840099,3840514,3840099,3840868,3840693,3840136,3840107,3840514,3840107,3840868,3840709,3840136,3840107,3840514,3840107,3840868,3841021,3840136,3840115,3840786,3840115,3840868,3840136,3840115,3840786,3840115,3840988,3840136,3840115,3840786,3840115,3840988,3840144,3840673,3840988,3840144,3840673,3840988,3840144,3840673,3840988,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840144,3840673,3840673,3840673,3840673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L19 W11/25; N=109; EHP=3728.000000; air:2x2,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x13,normal:18x14,fast:30x3,heavy:31x1,heavy:40x1,fast:58x4,fast:64x3,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x30,heavy:86x1,heavy:88x1,fast:98x3,medium:108x5,medium:123x5,heavy:127x1</t>
+          <t>L19 W11/25; N=109; EHP=9638.994904; air:2x4,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x1,medium:83x6,medium:108x5,medium:123x5,normal:17x13,normal:18x14,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3842136,3842673,3842242,3842019,3842668,3842253,3842136,3842673,3842242,3842019,3842668,3842325,3842136,3842673,3842242,3842019,3842668,3842541,3842136,3842673,3842466,3842091,3842668,3842541,3842136,3842673,3842466,3842091,3842668,3842565,3842136,3842673,3842466,3842099,3842868,3842645,3842136,3842673,3842514,3842099,3842868,3842645,3842136,3842673,3842514,3842099,3842868,3842693,3842136,3842673,3842514,3842107,3842868,3842709,3842136,3842673,3842514,3842107,3842868,3842709,3842136,3842673,3842786,3842107,3842868,3843021,3842136,3842673,3842786,3842115,3842988,3842136,3842673,3842786,3842115,3842988,3842136,3842673,3842115,3842988,3842144,3842673,3842988,3842144,3842673,3842988,3842144,3842673,3842988,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842673,3842673,3842673,3842673</t>
+          <t>3842136,3842019,3842242,3842019,3842668,3842253,3842136,3842019,3842242,3842019,3842668,3842325,3842136,3842019,3842242,3842019,3842668,3842541,3842136,3842091,3842466,3842091,3842668,3842541,3842136,3842091,3842466,3842091,3842668,3842565,3842136,3842099,3842466,3842099,3842868,3842645,3842136,3842099,3842514,3842099,3842868,3842645,3842136,3842099,3842514,3842099,3842868,3842693,3842136,3842107,3842514,3842107,3842868,3842709,3842136,3842107,3842514,3842107,3842868,3842709,3842136,3842107,3842786,3842107,3842868,3843021,3842136,3842115,3842786,3842115,3842988,3842136,3842115,3842786,3842115,3842988,3842136,3842115,3842115,3842988,3842144,3842673,3842988,3842144,3842673,3842988,3842144,3842673,3842988,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842144,3842673,3842673,3842673,3842673,3842673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L19 W12/25; N=115; EHP=3858.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x14,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x4,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x32,heavy:86x1,heavy:88x2,fast:98x3,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L19 W12/25; N=115; EHP=9977.039124; air:2x6,air:11x4,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x3,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x5,medium:108x6,medium:123x6,normal:17x14,normal:18x14,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3844136,3844673,3844242,3844019,3844668,3844253,3844136,3844673,3844242,3844019,3844668,3844253,3844136,3844673,3844242,3844019,3844668,3844325,3844136,3844673,3844242,3844091,3844668,3844541,3844136,3844673,3844466,3844091,3844668,3844565,3844136,3844673,3844466,3844091,3844668,3844645,3844136,3844673,3844466,3844099,3844868,3844645,3844136,3844673,3844514,3844099,3844868,3844693,3844136,3844673,3844514,3844099,3844868,3844693,3844136,3844673,3844514,3844107,3844868,3844709,3844136,3844673,3844786,3844107,3844868,3844709,3844136,3844673,3844786,3844107,3844868,3845021,3844136,3844673,3844786,3844115,3844988,3844136,3844673,3844786,3844115,3844988,3844144,3844673,3844115,3844988,3844144,3844673,3844988,3844144,3844673,3844988,3844144,3844673,3844988,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844673,3844673,3844673,3844673</t>
+          <t>3844136,3844019,3844242,3844019,3844668,3844253,3844136,3844019,3844242,3844019,3844668,3844253,3844136,3844019,3844242,3844019,3844668,3844325,3844136,3844091,3844242,3844091,3844668,3844541,3844136,3844091,3844466,3844091,3844668,3844565,3844136,3844091,3844466,3844091,3844668,3844645,3844136,3844099,3844466,3844099,3844868,3844645,3844136,3844099,3844514,3844099,3844868,3844693,3844136,3844099,3844514,3844099,3844868,3844693,3844136,3844107,3844514,3844107,3844868,3844709,3844136,3844107,3844786,3844107,3844868,3844709,3844136,3844107,3844786,3844107,3844868,3845021,3844136,3844115,3844786,3844115,3844988,3844136,3844115,3844786,3844115,3844988,3844144,3844115,3844115,3844988,3844144,3844673,3844988,3844144,3844673,3844988,3844144,3844673,3844988,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844144,3844673,3844673,3844673,3844673,3844673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L19 W13/25; N=121; EHP=4706.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x4,heavy:31x2,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x33,heavy:86x2,heavy:88x2,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L19 W13/25; N=121; EHP=12171.890145; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x4,heavy:31x2,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x14,normal:18x15,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3846136,3846673,3846242,3846019,3846668,3846253,3846136,3846673,3846242,3846019,3846668,3846253,3846136,3846673,3846242,3846019,3846668,3846325,3846136,3846673,3846466,3846091,3846668,3846325,3846136,3846673,3846466,3846091,3846668,3846541,3846136,3846673,3846466,3846091,3846668,3846565,3846136,3846673,3846466,3846099,3846668,3846645,3846136,3846673,3846514,3846099,3846868,3846645,3846136,3846673,3846514,3846099,3846868,3846693,3846136,3846673,3846514,3846107,3846868,3846693,3846136,3846673,3846514,3846107,3846868,3846709,3846136,3846673,3846786,3846107,3846868,3847021,3846136,3846673,3846786,3846115,3846868,3846136,3846673,3846786,3846115,3846988,3846136,3846673,3846786,3846115,3846988,3846136,3846673,3846988,3846144,3846673,3846988,3846144,3846673,3846988,3846144,3846673,3846988,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846673,3846673,3846673,3846673</t>
+          <t>3846136,3846019,3846242,3846019,3846668,3846253,3846136,3846019,3846242,3846019,3846668,3846253,3846136,3846019,3846242,3846019,3846668,3846325,3846136,3846091,3846466,3846091,3846668,3846325,3846136,3846091,3846466,3846091,3846668,3846541,3846136,3846091,3846466,3846091,3846668,3846565,3846136,3846099,3846466,3846099,3846668,3846645,3846136,3846099,3846514,3846099,3846868,3846645,3846136,3846099,3846514,3846099,3846868,3846693,3846136,3846107,3846514,3846107,3846868,3846693,3846136,3846107,3846514,3846107,3846868,3846709,3846136,3846107,3846786,3846107,3846868,3847021,3846136,3846115,3846786,3846115,3846868,3846136,3846115,3846786,3846115,3846988,3846136,3846115,3846786,3846115,3846988,3846136,3846673,3846988,3846144,3846673,3846988,3846144,3846673,3846988,3846144,3846673,3846988,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846144,3846673,3846673,3846673,3846673,3846673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L19 W14/25; N=127; EHP=5677.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x15,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x7,swarm:84x35,heavy:86x2,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L19 W14/25; N=127; EHP=14675.692088; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x7,medium:108x6,medium:123x6,normal:17x16,normal:18x15,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3848136,3848673,3848242,3848019,3848668,3848253,3848542,3848136,3848673,3848242,3848019,3848668,3848253,3848136,3848673,3848242,3848019,3848668,3848325,3848136,3848673,3848242,3848091,3848668,3848325,3848136,3848673,3848466,3848091,3848668,3848541,3848136,3848673,3848466,3848091,3848668,3848565,3848136,3848673,3848466,3848099,3848868,3848565,3848136,3848673,3848466,3848099,3848868,3848645,3848136,3848673,3848514,3848099,3848868,3848693,3848136,3848673,3848514,3848107,3848868,3848693,3848136,3848673,3848514,3848107,3848868,3848709,3848136,3848673,3848514,3848107,3848868,3849021,3848136,3848673,3848786,3848107,3848988,3849021,3848136,3848673,3848786,3848115,3848988,3848136,3848673,3848786,3848115,3848988,3848136,3848673,3848115,3848988,3848144,3848673,3848988,3848144,3848673,3848988,3848144,3848673,3848988,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848673,3848673,3848673,3848673,3848673</t>
+          <t>3848136,3848019,3848242,3848019,3848668,3848253,3848542,3848136,3848019,3848242,3848019,3848668,3848253,3848136,3848019,3848242,3848019,3848668,3848325,3848136,3848091,3848242,3848091,3848668,3848325,3848136,3848091,3848466,3848091,3848668,3848541,3848136,3848091,3848466,3848091,3848668,3848565,3848136,3848099,3848466,3848099,3848868,3848565,3848136,3848099,3848466,3848099,3848868,3848645,3848136,3848099,3848514,3848099,3848868,3848693,3848136,3848107,3848514,3848107,3848868,3848693,3848136,3848107,3848514,3848107,3848868,3848709,3848136,3848107,3848514,3848107,3848868,3849021,3848136,3848107,3848786,3848107,3848988,3849021,3848136,3848115,3848786,3848115,3848988,3848136,3848115,3848786,3848115,3848988,3848136,3848115,3848115,3848988,3848144,3848673,3848988,3848144,3848673,3848988,3848144,3848673,3848988,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848144,3848673,3848673,3848673,3848673,3848673,3848673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L19 W15/25; N=133; EHP=9908.000000; air:2x3,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,elite:67x1,heavy:67x1,heavy:70x2,heavy:80x1,medium:83x6,swarm:84x37,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x7,heavy:127x2</t>
+          <t>L19 W15/25; N=133; EHP=25611.372428; air:2x6,air:11x6,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x2,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x7,normal:17x16,normal:18x16,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3850136,3850673,3850242,3850019,3850668,3850253,3850136,3850673,3850242,3850019,3850668,3850253,3850136,3850673,3850242,3850019,3850668,3850325,3850136,3850673,3850242,3850091,3850668,3850325,3850136,3850673,3850466,3850091,3850668,3850541,3850136,3850673,3850466,3850091,3850668,3850541,3850136,3850673,3850466,3850091,3850668,3850565,3850136,3850673,3850466,3850099,3850868,3850565,3850136,3850673,3850514,3850099,3850868,3850645,3850136,3850673,3850514,3850099,3850868,3850693,3850136,3850673,3850514,3850107,3850868,3850709,3850136,3850673,3850514,3850107,3850868,3851021,3850136,3850673,3850786,3850107,3850868,3851021,3850136,3850673,3850786,3850115,3850868,3850136,3850673,3850786,3850115,3850988,3850136,3850673,3850786,3850115,3850988,3850136,3850673,3850115,3850988,3850136,3850673,3850988,3850144,3850673,3850988,3850144,3850673,3850988,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850673,3850673,3850673</t>
+          <t>3850136,3850019,3850242,3850019,3850668,3850253,3850136,3850019,3850242,3850019,3850668,3850253,3850136,3850019,3850242,3850019,3850668,3850325,3850136,3850091,3850242,3850091,3850668,3850325,3850136,3850091,3850466,3850091,3850668,3850541,3850136,3850091,3850466,3850091,3850668,3850541,3850136,3850091,3850466,3850091,3850668,3850565,3850136,3850099,3850466,3850099,3850868,3850565,3850136,3850099,3850514,3850099,3850868,3850645,3850136,3850099,3850514,3850099,3850868,3850693,3850136,3850107,3850514,3850107,3850868,3850709,3850136,3850107,3850514,3850107,3850868,3851021,3850136,3850107,3850786,3850107,3850868,3851021,3850136,3850115,3850786,3850115,3850868,3850136,3850115,3850786,3850115,3850988,3850136,3850115,3850786,3850115,3850988,3850136,3850115,3850115,3850988,3850136,3850673,3850988,3850144,3850673,3850988,3850144,3850673,3850988,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850144,3850673,3850673,3850673,3850673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L19 W16/25; N=139; EHP=10107.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x4,normal:17x18,normal:18x17,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x38,heavy:86x1,heavy:88x1,fast:98x4,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L19 W16/25; N=139; EHP=26140.008433; air:2x6,air:11x8,air:12x6,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x7,medium:108x7,medium:123x6,normal:17x18,normal:18x17,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3852136,3852673,3852242,3852019,3852668,3852253,3852136,3852673,3852242,3852019,3852668,3852325,3852136,3852673,3852242,3852019,3852668,3852325,3852136,3852673,3852242,3852091,3852668,3852541,3852136,3852673,3852242,3852091,3852668,3852541,3852136,3852673,3852466,3852091,3852668,3852565,3852136,3852673,3852466,3852099,3852668,3852565,3852136,3852673,3852466,3852099,3852868,3852645,3852136,3852673,3852466,3852099,3852868,3852645,3852136,3852673,3852514,3852099,3852868,3852693,3852136,3852673,3852514,3852107,3852868,3852709,3852136,3852673,3852514,3852107,3852868,3852709,3852136,3852673,3852514,3852107,3852868,3853021,3852136,3852673,3852786,3852115,3852868,3853021,3852136,3852673,3852786,3852115,3852988,3852136,3852673,3852786,3852115,3852988,3852136,3852673,3852786,3852115,3852988,3852136,3852673,3852988,3852144,3852673,3852988,3852144,3852673,3852988,3852144,3852673,3852988,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852673,3852673,3852673,3852673</t>
+          <t>3852136,3852019,3852242,3852019,3852668,3852253,3852136,3852019,3852242,3852019,3852668,3852325,3852136,3852019,3852242,3852019,3852668,3852325,3852136,3852091,3852242,3852091,3852668,3852541,3852136,3852091,3852242,3852091,3852668,3852541,3852136,3852091,3852466,3852091,3852668,3852565,3852136,3852099,3852466,3852099,3852668,3852565,3852136,3852099,3852466,3852099,3852868,3852645,3852136,3852099,3852466,3852099,3852868,3852645,3852136,3852099,3852514,3852099,3852868,3852693,3852136,3852107,3852514,3852107,3852868,3852709,3852136,3852107,3852514,3852107,3852868,3852709,3852136,3852107,3852514,3852107,3852868,3853021,3852136,3852115,3852786,3852115,3852868,3853021,3852136,3852115,3852786,3852115,3852988,3852136,3852115,3852786,3852115,3852988,3852136,3852115,3852786,3852115,3852988,3852136,3852673,3852988,3852144,3852673,3852988,3852144,3852673,3852988,3852144,3852673,3852988,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852144,3852673,3852673,3852673,3852673,3852673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L19 W17/25; N=145; EHP=10310.000000; air:2x3,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x18,fast:30x5,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L19 W17/25; N=145; EHP=26650.423219; air:2x6,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x5,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x23 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3854136,3854673,3854242,3854019,3854668,3854253,3854136,3854673,3854242,3854019,3854668,3854253,3854136,3854673,3854242,3854019,3854668,3854325,3854136,3854673,3854242,3854019,3854668,3854541,3854136,3854673,3854466,3854091,3854668,3854541,3854136,3854673,3854466,3854091,3854668,3854565,3854136,3854673,3854466,3854091,3854668,3854565,3854136,3854673,3854466,3854099,3854868,3854645,3854136,3854673,3854466,3854099,3854868,3854645,3854136,3854673,3854514,3854099,3854868,3854693,3854136,3854673,3854514,3854099,3854868,3854693,3854136,3854673,3854514,3854107,3854868,3854709,3854136,3854673,3854514,3854107,3854868,3854709,3854136,3854673,3854786,3854107,3854868,3855021,3854136,3854673,3854786,3854107,3854988,3855021,3854136,3854673,3854786,3854115,3854988,3854136,3854673,3854786,3854115,3854988,3854136,3854673,3854786,3854115,3854988,3854144,3854673,3854988,3854144,3854673,3854988,3854144,3854673,3854988,3854144,3854673,3854988,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854673,3854673,3854673,3854673,3854673,3854673</t>
+          <t>3854136,3854019,3854242,3854019,3854668,3854253,3854136,3854019,3854242,3854019,3854668,3854253,3854136,3854019,3854242,3854019,3854668,3854325,3854136,3854019,3854242,3854019,3854668,3854541,3854136,3854091,3854466,3854091,3854668,3854541,3854136,3854091,3854466,3854091,3854668,3854565,3854136,3854091,3854466,3854091,3854668,3854565,3854136,3854099,3854466,3854099,3854868,3854645,3854136,3854099,3854466,3854099,3854868,3854645,3854136,3854099,3854514,3854099,3854868,3854693,3854136,3854099,3854514,3854099,3854868,3854693,3854136,3854107,3854514,3854107,3854868,3854709,3854136,3854107,3854514,3854107,3854868,3854709,3854136,3854107,3854786,3854107,3854868,3855021,3854136,3854107,3854786,3854107,3854988,3855021,3854136,3854115,3854786,3854115,3854988,3854136,3854115,3854786,3854115,3854988,3854136,3854115,3854786,3854115,3854988,3854144,3854673,3854988,3854144,3854673,3854988,3854144,3854673,3854988,3854144,3854673,3854988,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854144,3854673,3854673,3854673,3854673,3854673,3854673,3854673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L19 W18/25; N=151; EHP=11014.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x3,normal:17x18,normal:18x18,fast:30x4,heavy:31x2,heavy:40x1,fast:58x5,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x42,heavy:86x2,heavy:88x2,fast:98x5,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L19 W18/25; N=151; EHP=28474.971478; air:2x8,air:11x6,air:12x8,air:13x8,air:14x6,fast:30x4,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x8,normal:17x18,normal:18x18,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3856136,3856673,3856242,3856019,3856668,3856253,3856136,3856673,3856242,3856019,3856668,3856253,3856136,3856673,3856242,3856019,3856668,3856325,3856136,3856673,3856242,3856019,3856668,3856325,3856136,3856673,3856466,3856091,3856668,3856541,3856136,3856673,3856466,3856091,3856668,3856541,3856136,3856673,3856466,3856091,3856668,3856565,3856136,3856673,3856466,3856091,3856668,3856565,3856136,3856673,3856466,3856099,3856868,3856645,3856136,3856673,3856514,3856099,3856868,3856645,3856136,3856673,3856514,3856099,3856868,3856693,3856136,3856673,3856514,3856107,3856868,3856693,3856136,3856673,3856514,3856107,3856868,3856709,3856136,3856673,3856514,3856107,3856868,3856709,3856136,3856673,3856786,3856107,3856868,3857021,3856136,3856673,3856786,3856115,3856868,3856136,3856673,3856786,3856115,3856988,3856136,3856673,3856786,3856115,3856988,3856136,3856673,3856115,3856988,3856144,3856673,3856988,3856144,3856673,3856988,3856144,3856673,3856988,3856144,3856673,3856988,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856673,3856673,3856673,3856673</t>
+          <t>3856136,3856019,3856242,3856019,3856668,3856253,3856136,3856019,3856242,3856019,3856668,3856253,3856136,3856019,3856242,3856019,3856668,3856325,3856136,3856019,3856242,3856019,3856668,3856325,3856136,3856091,3856466,3856091,3856668,3856541,3856136,3856091,3856466,3856091,3856668,3856541,3856136,3856091,3856466,3856091,3856668,3856565,3856136,3856091,3856466,3856091,3856668,3856565,3856136,3856099,3856466,3856099,3856868,3856645,3856136,3856099,3856514,3856099,3856868,3856645,3856136,3856099,3856514,3856099,3856868,3856693,3856136,3856107,3856514,3856107,3856868,3856693,3856136,3856107,3856514,3856107,3856868,3856709,3856136,3856107,3856514,3856107,3856868,3856709,3856136,3856107,3856786,3856107,3856868,3857021,3856136,3856115,3856786,3856115,3856868,3856136,3856115,3856786,3856115,3856988,3856136,3856115,3856786,3856115,3856988,3856136,3856115,3856115,3856988,3856144,3856673,3856988,3856144,3856673,3856988,3856144,3856673,3856988,3856144,3856673,3856988,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856144,3856673,3856673,3856673,3856673,3856673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L19 W19/25; N=157; EHP=12758.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x19,normal:18x20,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x43,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x7,heavy:127x1</t>
+          <t>L19 W19/25; N=157; EHP=32990.525568; air:2x8,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x4,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x8,medium:108x8,medium:123x7,normal:17x19,normal:18x20,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3858136,3858673,3858242,3858019,3858668,3858253,3858542,3858136,3858673,3858242,3858019,3858668,3858253,3858136,3858673,3858242,3858019,3858668,3858325,3858136,3858673,3858242,3858019,3858668,3858325,3858136,3858673,3858242,3858091,3858668,3858541,3858136,3858673,3858466,3858091,3858668,3858541,3858136,3858673,3858466,3858091,3858668,3858565,3858136,3858673,3858466,3858091,3858668,3858565,3858136,3858673,3858466,3858099,3858868,3858645,3858136,3858673,3858514,3858099,3858868,3858645,3858136,3858673,3858514,3858099,3858868,3858693,3858136,3858673,3858514,3858099,3858868,3858693,3858136,3858673,3858514,3858107,3858868,3858709,3858136,3858673,3858514,3858107,3858868,3858709,3858136,3858673,3858786,3858107,3858868,3859021,3858136,3858673,3858786,3858107,3858868,3859021,3858136,3858673,3858786,3858115,3858988,3858136,3858673,3858786,3858115,3858988,3858136,3858673,3858786,3858115,3858988,3858144,3858673,3858115,3858988,3858144,3858673,3858988,3858144,3858673,3858988,3858144,3858673,3858988,3858144,3858673,3858988,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858673,3858673,3858673,3858673,3858673,3858673,3858673</t>
+          <t>3858136,3858019,3858242,3858019,3858668,3858253,3858542,3858136,3858019,3858242,3858019,3858668,3858253,3858136,3858019,3858242,3858019,3858668,3858325,3858136,3858019,3858242,3858019,3858668,3858325,3858136,3858091,3858242,3858091,3858668,3858541,3858136,3858091,3858466,3858091,3858668,3858541,3858136,3858091,3858466,3858091,3858668,3858565,3858136,3858091,3858466,3858091,3858668,3858565,3858136,3858099,3858466,3858099,3858868,3858645,3858136,3858099,3858514,3858099,3858868,3858645,3858136,3858099,3858514,3858099,3858868,3858693,3858136,3858099,3858514,3858099,3858868,3858693,3858136,3858107,3858514,3858107,3858868,3858709,3858136,3858107,3858514,3858107,3858868,3858709,3858136,3858107,3858786,3858107,3858868,3859021,3858136,3858107,3858786,3858107,3858868,3859021,3858136,3858115,3858786,3858115,3858988,3858136,3858115,3858786,3858115,3858988,3858136,3858115,3858786,3858115,3858988,3858144,3858115,3858115,3858988,3858144,3858673,3858988,3858144,3858673,3858988,3858144,3858673,3858988,3858144,3858673,3858988,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858144,3858673,3858673,3858673,3858673,3858673,3858673,3858673,3858673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L19 W20/25; N=163; EHP=21417.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L19 W20/25; N=163; EHP=55375.207200; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x4,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10018317,10018327,10018319,10048650,10018326,10018320,10018317,10018327,10018319,10048650,10018326,10018320,10018317,10018327,10018319,10048650,10018326,10018321,10018317,10018327,10018319,10048650,10018326,10018321,10018317,10018327,10018319,10018314,10018326,10045200,10018317,10018327,10018322,10018314,10018326,10045200,10018317,10018327,10018322,10018314,10018326,10018324,10018317,10018327,10018322,10018314,10018326,10018324,10018317,10018327,10018322,10048651,10018331,10018325,10018317,10018327,10018322,10048651,10018331,10018325,10018317,10018327,10018323,10048651,10018331,10018328,10018317,10018327,10018323,10048651,10018331,10018328,10018317,10018327,10018323,10018315,10018331,10018329,10018317,10018327,10018323,10018315,10018331,10018329,10018317,10018327,10018323,10018315,10018331,10018333,10018317,10018327,10018330,10018315,10018331,10018333,10018317,10018327,10018330,10018316,10018332,10018317,10018327,10018330,10018316,10018332,10018317,10018327,10018330,10018316,10018332,10018317,10018327,10018330,10018316,10018332,10018318,10018327,10018332,10018318,10018327,10018332,10018318,10018327,10018332,10018318,10018327,10018332,10018318,10018327,10018332,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018327,10018327,10018327,10018327,10018327,10018327</t>
+          <t>10018317,10048650,10018319,10048650,10018326,10018320,10018317,10048650,10018319,10048650,10018326,10018320,10018317,10048650,10018319,10048650,10018326,10018321,10018317,10048650,10018319,10048650,10018326,10018321,10018317,10018314,10018319,10018314,10018326,10045200,10018317,10018314,10018322,10018314,10018326,10045200,10018317,10018314,10018322,10018314,10018326,10018324,10018317,10018314,10018322,10018314,10018326,10018324,10018317,10048651,10018322,10048651,10018331,10018325,10018317,10048651,10018322,10048651,10018331,10018325,10018317,10048651,10018323,10048651,10018331,10018328,10018317,10048651,10018323,10048651,10018331,10018328,10018317,10018315,10018323,10018315,10018331,10018329,10018317,10018315,10018323,10018315,10018331,10018329,10018317,10018315,10018323,10018315,10018331,10018333,10018317,10018315,10018330,10018315,10018331,10018333,10018317,10018316,10018330,10018316,10018332,10018317,10018316,10018330,10018316,10018332,10018317,10018316,10018330,10018316,10018332,10018317,10018316,10018330,10018316,10018332,10018318,10018327,10018332,10018318,10018327,10018332,10018318,10018327,10018332,10018318,10018327,10018332,10018318,10018327,10018332,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018318,10018327,10018327,10018327,10018327,10018327,10018327,10018327</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L19 W21/25; N=169; EHP=21846.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x20,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L19 W21/25; N=169; EHP=56476.875234; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x9,normal:17x20,normal:18x21,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10018337,10018348,10018339,10048652,10018347,10018340,10018337,10018348,10018339,10048652,10018347,10018340,10018337,10018348,10018339,10048652,10018347,10018341,10018337,10018348,10018339,10048652,10018347,10018341,10018337,10018348,10018339,10018334,10018347,10018344,10018337,10018348,10018342,10018334,10018347,10018344,10018337,10018348,10018342,10018334,10018347,10018345,10018337,10018348,10018342,10018334,10018347,10018345,10018337,10018348,10018342,10048653,10018347,10018346,10018337,10018348,10018342,10048653,10018351,10018346,10018337,10018348,10018343,10048653,10018351,10018346,10018337,10018348,10018343,10048653,10018351,10018349,10018337,10018348,10018343,10018335,10018351,10018349,10018337,10018348,10018343,10018335,10018351,10045201,10018337,10018348,10018343,10018335,10018351,10045201,10018337,10018348,10018350,10018335,10018351,10018353,10018337,10018348,10018350,10018336,10018351,10018353,10018337,10018348,10018350,10018336,10018351,10018337,10018348,10018350,10018336,10018352,10018337,10018348,10018350,10018336,10018352,10018337,10018348,10018350,10018336,10018352,10018338,10018348,10018352,10018338,10018348,10018352,10018338,10018348,10018352,10018338,10018348,10018352,10018338,10018348,10018352,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018348,10018348,10018348,10018348,10018348,10018348,10018348,10018348</t>
+          <t>10018337,10048652,10018339,10048652,10018347,10018340,10018337,10048652,10018339,10048652,10018347,10018340,10018337,10048652,10018339,10048652,10018347,10018341,10018337,10048652,10018339,10048652,10018347,10018341,10018337,10018334,10018339,10018334,10018347,10018344,10018337,10018334,10018342,10018334,10018347,10018344,10018337,10018334,10018342,10018334,10018347,10018345,10018337,10018334,10018342,10018334,10018347,10018345,10018337,10048653,10018342,10048653,10018347,10018346,10018337,10048653,10018342,10048653,10018351,10018346,10018337,10048653,10018343,10048653,10018351,10018346,10018337,10048653,10018343,10048653,10018351,10018349,10018337,10018335,10018343,10018335,10018351,10018349,10018337,10018335,10018343,10018335,10018351,10045201,10018337,10018335,10018343,10018335,10018351,10045201,10018337,10018335,10018350,10018335,10018351,10018353,10018337,10018336,10018350,10018336,10018351,10018353,10018337,10018336,10018350,10018336,10018351,10018337,10018336,10018350,10018336,10018352,10018337,10018336,10018350,10018336,10018352,10018337,10018336,10018350,10018336,10018352,10018338,10018348,10018352,10018338,10018348,10018352,10018338,10018348,10018352,10018338,10018348,10018352,10018338,10018348,10018352,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018338,10018348,10018348,10018348,10018348,10018348,10018348,10018348,10018348,10018348</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L19 W22/25; N=175; EHP=22283.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x5,normal:17x21,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x9,swarm:84x49,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L19 W22/25; N=175; EHP=57614.711080; air:2x8,air:11x8,air:12x8,air:13x8,air:14x10,fast:30x5,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x8,normal:17x21,normal:18x20,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10018357,10018368,10018359,10048654,10018367,10018360,10018357,10018368,10018359,10048654,10018367,10018360,10018357,10018368,10018359,10048654,10018367,10018360,10018357,10018368,10018359,10048654,10018367,10018361,10018357,10018368,10018359,10048654,10018367,10018361,10018357,10018368,10018362,10018354,10018367,10018364,10018357,10018368,10018362,10018354,10018367,10018364,10018357,10018368,10018362,10018354,10018367,10018365,10018357,10018368,10018362,10018354,10018367,10018365,10018357,10018368,10018362,10048655,10018372,10018366,10018357,10018368,10018362,10048655,10018372,10018366,10018357,10018368,10018363,10048655,10018372,10018369,10018357,10018368,10018363,10048655,10018372,10018369,10018357,10018368,10018363,10048655,10018372,10018369,10018357,10018368,10018363,10018355,10018372,10018370,10018357,10018368,10018363,10018355,10018372,10018370,10018357,10018368,10018371,10018355,10018372,10018374,10018357,10018368,10018371,10018355,10018372,10018374,10018357,10018368,10018371,10018356,10018373,10018357,10018368,10018371,10018356,10018373,10018357,10018368,10018371,10018356,10018373,10018358,10018368,10018356,10018373,10018358,10018368,10018373,10018358,10018368,10018373,10018358,10018368,10018373,10018358,10018368,10018373,10018358,10018368,10018373,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018368,10018368,10018368,10018368,10018368,10018368,10018368</t>
+          <t>10018357,10048654,10018359,10048654,10018367,10018360,10018357,10048654,10018359,10048654,10018367,10018360,10018357,10048654,10018359,10048654,10018367,10018360,10018357,10048654,10018359,10048654,10018367,10018361,10018357,10048654,10018359,10048654,10018367,10018361,10018357,10018354,10018362,10018354,10018367,10018364,10018357,10018354,10018362,10018354,10018367,10018364,10018357,10018354,10018362,10018354,10018367,10018365,10018357,10018354,10018362,10018354,10018367,10018365,10018357,10048655,10018362,10048655,10018372,10018366,10018357,10048655,10018362,10048655,10018372,10018366,10018357,10048655,10018363,10048655,10018372,10018369,10018357,10048655,10018363,10048655,10018372,10018369,10018357,10048655,10018363,10048655,10018372,10018369,10018357,10018355,10018363,10018355,10018372,10018370,10018357,10018355,10018363,10018355,10018372,10018370,10018357,10018355,10018371,10018355,10018372,10018374,10018357,10018355,10018371,10018355,10018372,10018374,10018357,10018356,10018371,10018356,10018373,10018357,10018356,10018371,10018356,10018373,10018357,10018356,10018371,10018356,10018373,10018358,10018356,10018356,10018373,10018358,10018368,10018373,10018358,10018368,10018373,10018358,10018368,10018373,10018358,10018368,10018373,10018358,10018368,10018373,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018358,10018368,10018368,10018368,10018368,10018368,10018368,10018368,10018368</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L19 W23/25; N=181; EHP=22729.000000; air:2x5,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x21,normal:18x22,fast:30x5,heavy:31x3,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x3,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L19 W23/25; N=181; EHP=58773.769373; air:2x10,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x6,fast:64x5,fast:98x5,heavy:31x3,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x21,normal:18x22,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10018378,10018389,10018380,10048656,10018388,10018381,10018378,10018389,10018380,10048656,10018388,10018381,10018378,10018389,10018380,10048656,10018388,10018381,10018378,10018389,10018380,10048656,10018388,10018382,10018378,10018389,10018380,10048656,10018388,10018382,10018378,10018389,10018380,10018375,10018388,10018382,10018378,10018389,10018383,10018375,10018388,10018385,10018378,10018389,10018383,10018375,10018388,10018385,10018378,10018389,10018383,10018375,10018388,10018386,10018378,10018389,10018383,10048657,10018393,10018386,10018378,10018389,10018383,10048657,10018393,10018387,10018378,10018389,10018384,10048657,10018393,10018387,10018378,10018389,10018384,10048657,10018393,10018390,10018378,10018389,10018384,10018376,10018393,10018390,10018378,10018389,10018384,10018376,10018393,10018391,10018378,10018389,10018384,10018376,10018393,10018391,10018378,10018389,10018384,10018376,10018393,10018395,10018378,10018389,10018392,10018376,10018393,10018395,10018378,10018389,10018392,10018377,10018394,10018378,10018389,10018392,10018377,10018394,10018378,10018389,10018392,10018377,10018394,10018378,10018389,10018392,10018377,10018394,10018378,10018389,10018394,10018379,10018389,10018394,10018379,10018389,10018394,10018379,10018389,10018394,10018379,10018389,10018394,10018379,10018389,10018394,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018389,10018389,10018389,10018389,10018389,10018389,10018389</t>
+          <t>10018378,10048656,10018380,10048656,10018388,10018381,10018378,10048656,10018380,10048656,10018388,10018381,10018378,10048656,10018380,10048656,10018388,10018381,10018378,10048656,10018380,10048656,10018388,10018382,10018378,10048656,10018380,10048656,10018388,10018382,10018378,10018375,10018380,10018375,10018388,10018382,10018378,10018375,10018383,10018375,10018388,10018385,10018378,10018375,10018383,10018375,10018388,10018385,10018378,10018375,10018383,10018375,10018388,10018386,10018378,10048657,10018383,10048657,10018393,10018386,10018378,10048657,10018383,10048657,10018393,10018387,10018378,10048657,10018384,10048657,10018393,10018387,10018378,10048657,10018384,10048657,10018393,10018390,10018378,10018376,10018384,10018376,10018393,10018390,10018378,10018376,10018384,10018376,10018393,10018391,10018378,10018376,10018384,10018376,10018393,10018391,10018378,10018376,10018384,10018376,10018393,10018395,10018378,10018376,10018392,10018376,10018393,10018395,10018378,10018377,10018392,10018377,10018394,10018378,10018377,10018392,10018377,10018394,10018378,10018377,10018392,10018377,10018394,10018378,10018377,10018392,10018377,10018394,10018378,10018389,10018394,10018379,10018389,10018394,10018379,10018389,10018394,10018379,10018389,10018394,10018379,10018389,10018394,10018379,10018389,10018394,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018379,10018389,10018389,10018389,10018389,10018389,10018389,10018389,10018389</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L19 W24/25; N=187; EHP=24339.000000; air:2x5,air:11x4,air:12x4,air:13x5,air:14x4,normal:17x23,normal:18x22,fast:30x6,heavy:31x3,heavy:40x3,fast:58x5,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x52,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x10,heavy:127x2</t>
+          <t>L19 W24/25; N=187; EHP=62915.188522; air:2x10,air:11x8,air:12x8,air:13x10,air:14x8,fast:30x6,fast:58x5,fast:64x6,fast:98x5,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x10,normal:17x23,normal:18x22,swarm:84x30 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10018399,10018410,10018401,10048658,10018409,10018402,10018417,10018399,10018410,10018401,10048658,10018409,10018402,10018399,10018410,10018401,10048658,10018409,10018403,10018399,10018410,10018401,10048658,10018409,10018403,10018399,10018410,10018401,10018396,10018409,10018403,10018399,10018410,10018401,10018396,10018409,10018406,10018399,10018410,10018404,10018396,10018409,10018406,10018399,10018410,10018404,10018396,10018409,10018407,10018399,10018410,10018404,10018396,10018409,10018407,10018399,10018410,10018404,10048659,10018414,10018407,10018399,10018410,10018404,10048659,10018414,10018408,10018399,10018410,10018404,10048659,10018414,10018408,10018399,10018410,10018405,10048659,10018414,10018411,10018399,10018410,10018405,10018397,10018414,10018411,10018399,10018410,10018405,10018397,10018414,10018412,10018399,10018410,10018405,10018397,10018414,10018412,10018399,10018410,10018405,10018397,10018414,10018416,10018399,10018410,10018413,10018397,10018414,10018416,10018399,10018410,10018413,10018398,10018414,10018416,10018399,10018410,10018413,10018398,10018415,10018399,10018410,10018413,10018398,10018415,10018399,10018410,10018413,10018398,10018415,10018400,10018410,10018413,10018398,10018415,10018400,10018410,10018415,10018400,10018410,10018415,10018400,10018410,10018415,10018400,10018410,10018415,10018400,10018410,10018415,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018410,10018410,10018410,10018410,10018410,10018410,10018410,10018410,10018410</t>
+          <t>10018399,10048658,10018401,10048658,10018409,10018402,10018417,10018399,10048658,10018401,10048658,10018409,10018402,10018399,10048658,10018401,10048658,10018409,10018403,10018399,10048658,10018401,10048658,10018409,10018403,10018399,10018396,10018401,10018396,10018409,10018403,10018399,10018396,10018401,10018396,10018409,10018406,10018399,10018396,10018404,10018396,10018409,10018406,10018399,10018396,10018404,10018396,10018409,10018407,10018399,10018396,10018404,10018396,10018409,10018407,10018399,10048659,10018404,10048659,10018414,10018407,10018399,10048659,10018404,10048659,10018414,10018408,10018399,10048659,10018404,10048659,10018414,10018408,10018399,10048659,10018405,10048659,10018414,10018411,10018399,10018397,10018405,10018397,10018414,10018411,10018399,10018397,10018405,10018397,10018414,10018412,10018399,10018397,10018405,10018397,10018414,10018412,10018399,10018397,10018405,10018397,10018414,10018416,10018399,10018397,10018413,10018397,10018414,10018416,10018399,10018398,10018413,10018398,10018414,10018416,10018399,10018398,10018413,10018398,10018415,10018399,10018398,10018413,10018398,10018415,10018399,10018398,10018413,10018398,10018415,10018400,10018398,10018413,10018398,10018415,10018400,10018410,10018415,10018400,10018410,10018415,10018400,10018410,10018415,10018400,10018410,10018415,10018400,10018410,10018415,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018400,10018410,10018410,10018410,10018410,10018410,10018410,10018410,10018410,10018410,10018410</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L19 W25/25; N=193; EHP=48578.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x22,normal:18x23,fast:30x6,heavy:31x2,heavy:40x3,fast:58x6,fast:64x5,heavy:67x2,heavy:70x3,heavy:80x2,medium:83x9,swarm:84x54,heavy:86x2,heavy:88x2,fast:98x6,medium:108x10,medium:123x9,heavy:127x3,boss:132x1</t>
+          <t>L19 W25/25; N=193; EHP=125565.326175; air:2x8,air:11x10,air:12x8,air:13x10,air:14x10,boss:132x1,fast:30x6,fast:58x6,fast:64x5,fast:98x6,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x10,medium:123x9,normal:17x22,normal:18x23,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L19/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L19/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>244</v>
+        <v>350</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>237</v>
+        <v>310</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>223</v>
+        <v>360</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>216</v>
+        <v>300</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>209</v>
+        <v>280</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>202</v>
+        <v>360</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>195</v>
+        <v>290</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>181</v>
+        <v>280</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>174</v>
+        <v>300</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>167</v>
+        <v>270</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>160</v>
+        <v>360</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>153</v>
+        <v>280</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>146</v>
+        <v>250</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>139</v>
+        <v>200</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>132</v>
+        <v>300</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
